--- a/excel/hmd_Continuous_mix_uv.xlsx
+++ b/excel/hmd_Continuous_mix_uv.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamilton\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6395F44D-3F63-478D-9C2F-383C9A046373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D4809E-DEA2-42B9-8337-8D76535214E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7815" yWindow="1350" windowWidth="18285" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="2820" windowWidth="18285" windowHeight="12375" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="非均布" sheetId="1" r:id="rId1"/>
+    <sheet name="均布" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -345,51 +348,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>0.46223048899581587</v>
+        <v>-1.0632338851745744</v>
       </c>
       <c r="C2">
-        <v>0.10771397428265418</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>-1.5874827273872187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>0.7414843305775853</v>
+        <v>-1.7068144228696176</v>
       </c>
       <c r="C3">
-        <v>0.10755302697617214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-2.7658353111422564</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>0.9594169224328156</v>
+        <v>-1.9786565279849735</v>
       </c>
       <c r="C4">
-        <v>0.13945336740980985</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>-3.1892686058458337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
       </c>
       <c r="B5">
-        <v>1.11577452670605</v>
+        <v>-2.8065099380037095</v>
       </c>
       <c r="C5">
-        <v>0.033225698366309696</v>
+        <v>-4.3215924930392147</v>
       </c>
     </row>
   </sheetData>
@@ -409,10 +412,10 @@
         <v>0.0</v>
       </c>
       <c r="B2">
-        <v>0.5485370407997108</v>
+        <v>-1.354351002515349</v>
       </c>
       <c r="C2">
-        <v>0.0994826442473461</v>
+        <v>-2.0796152414764886</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -420,10 +423,10 @@
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>0.9381035225411772</v>
+        <v>-1.9492735688430844</v>
       </c>
       <c r="C3">
-        <v>0.03979939210849755</v>
+        <v>-2.964892722365196</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -431,10 +434,10 @@
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>1.4734388003905656</v>
+        <v>-2.5495507201737966</v>
       </c>
       <c r="C4">
-        <v>0.009290018065089556</v>
+        <v>-3.8629125846701275</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -442,10 +445,10 @@
         <v>-0.9030899869919435</v>
       </c>
       <c r="B5">
-        <v>1.9075209153874706</v>
+        <v>-3.151170197774894</v>
       </c>
       <c r="C5">
-        <v>0.19709074206385566</v>
+        <v>-4.764667648393757</v>
       </c>
     </row>
   </sheetData>
